--- a/lista_ubicaciones_tecnicas.xlsx
+++ b/lista_ubicaciones_tecnicas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5551" uniqueCount="2848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5556" uniqueCount="2845">
   <si>
     <t>Ubicación técnica</t>
   </si>
@@ -7494,25 +7494,16 @@
     <t>MEZCLADOR DE CAL FF2</t>
   </si>
   <si>
-    <t>FF3</t>
-  </si>
-  <si>
     <t>1100-100-010-020</t>
   </si>
   <si>
     <t>MOTORREDUCTOR DE CAL FF2</t>
   </si>
   <si>
-    <t>FF4</t>
-  </si>
-  <si>
     <t>1100-100-010-030</t>
   </si>
   <si>
     <t>SENSOR DE PH CAL FF2</t>
-  </si>
-  <si>
-    <t>FF5</t>
   </si>
   <si>
     <t>1100-100-020</t>
@@ -9028,7 +9019,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>2847</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9038,9 +9029,11 @@
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>2843</v>
+      </c>
       <c r="D2" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -9656,7 +9649,7 @@
         <v>81</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2828</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -9740,7 +9733,7 @@
         <v>81</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2828</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -9824,7 +9817,7 @@
         <v>81</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2828</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -10370,7 +10363,7 @@
         <v>214</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -10846,7 +10839,7 @@
         <v>214</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -10888,7 +10881,7 @@
         <v>214</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -11364,7 +11357,7 @@
         <v>363</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -12414,7 +12407,7 @@
         <v>363</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -12428,7 +12421,7 @@
         <v>363</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -12442,7 +12435,7 @@
         <v>363</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -12456,7 +12449,7 @@
         <v>363</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -12470,7 +12463,7 @@
         <v>363</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -12484,7 +12477,7 @@
         <v>363</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -12498,7 +12491,7 @@
         <v>363</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -12862,7 +12855,7 @@
         <v>363</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -12876,7 +12869,7 @@
         <v>363</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -12890,7 +12883,7 @@
         <v>363</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -12904,7 +12897,7 @@
         <v>363</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="279" spans="1:9">
@@ -12918,7 +12911,7 @@
         <v>363</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -12946,7 +12939,7 @@
         <v>363</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -12960,7 +12953,7 @@
         <v>363</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="283" spans="1:9">
@@ -12974,7 +12967,7 @@
         <v>363</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="284" spans="1:9">
@@ -12988,7 +12981,7 @@
         <v>363</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="285" spans="1:9">
@@ -13002,7 +12995,7 @@
         <v>363</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -13087,7 +13080,7 @@
         <v>363</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -13115,7 +13108,7 @@
         <v>363</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -13129,7 +13122,7 @@
         <v>363</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -13143,7 +13136,7 @@
         <v>363</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -13241,7 +13234,7 @@
         <v>363</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -13255,7 +13248,7 @@
         <v>363</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -13269,7 +13262,7 @@
         <v>363</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -13283,7 +13276,7 @@
         <v>363</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -13381,7 +13374,7 @@
         <v>363</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -13395,7 +13388,7 @@
         <v>363</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -13409,7 +13402,7 @@
         <v>363</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -13423,7 +13416,7 @@
         <v>363</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -13507,7 +13500,7 @@
         <v>363</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -13521,7 +13514,7 @@
         <v>363</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -13535,7 +13528,7 @@
         <v>363</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -13549,7 +13542,7 @@
         <v>363</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -13633,7 +13626,7 @@
         <v>363</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -13647,7 +13640,7 @@
         <v>363</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -13661,7 +13654,7 @@
         <v>363</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -13675,7 +13668,7 @@
         <v>363</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -13759,7 +13752,7 @@
         <v>363</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -13773,7 +13766,7 @@
         <v>363</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -13787,7 +13780,7 @@
         <v>363</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -13801,7 +13794,7 @@
         <v>363</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -13885,7 +13878,7 @@
         <v>363</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -13899,7 +13892,7 @@
         <v>363</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -13913,7 +13906,7 @@
         <v>363</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -13927,7 +13920,7 @@
         <v>363</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -14011,7 +14004,7 @@
         <v>363</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -14025,7 +14018,7 @@
         <v>363</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -14039,7 +14032,7 @@
         <v>363</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -14053,7 +14046,7 @@
         <v>363</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -14137,7 +14130,7 @@
         <v>363</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -14151,7 +14144,7 @@
         <v>363</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -14165,7 +14158,7 @@
         <v>363</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -14179,7 +14172,7 @@
         <v>363</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -14263,7 +14256,7 @@
         <v>363</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -14277,7 +14270,7 @@
         <v>363</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -14291,7 +14284,7 @@
         <v>363</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -14305,7 +14298,7 @@
         <v>363</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -14319,7 +14312,7 @@
         <v>363</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -14361,7 +14354,7 @@
         <v>363</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -14389,7 +14382,7 @@
         <v>363</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -14403,7 +14396,7 @@
         <v>363</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -14417,7 +14410,7 @@
         <v>363</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -14431,7 +14424,7 @@
         <v>363</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -14501,7 +14494,7 @@
         <v>363</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>2830</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -14515,7 +14508,7 @@
         <v>363</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>2830</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -14529,7 +14522,7 @@
         <v>363</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>2831</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -14543,7 +14536,7 @@
         <v>363</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>2832</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -14879,7 +14872,7 @@
         <v>825</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -15467,7 +15460,7 @@
         <v>825</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -15481,7 +15474,7 @@
         <v>825</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -15495,7 +15488,7 @@
         <v>825</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -15579,7 +15572,7 @@
         <v>825</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -15593,7 +15586,7 @@
         <v>825</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -15607,7 +15600,7 @@
         <v>825</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -15621,7 +15614,7 @@
         <v>825</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -15635,7 +15628,7 @@
         <v>825</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -15649,7 +15642,7 @@
         <v>825</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -15663,7 +15656,7 @@
         <v>825</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -15677,7 +15670,7 @@
         <v>825</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -15691,7 +15684,7 @@
         <v>825</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -15705,7 +15698,7 @@
         <v>825</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -15719,7 +15712,7 @@
         <v>825</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -15733,7 +15726,7 @@
         <v>825</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -15747,7 +15740,7 @@
         <v>825</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -15761,7 +15754,7 @@
         <v>825</v>
       </c>
       <c r="D482" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -15775,7 +15768,7 @@
         <v>825</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -15789,7 +15782,7 @@
         <v>825</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -15817,7 +15810,7 @@
         <v>825</v>
       </c>
       <c r="D486" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -15831,7 +15824,7 @@
         <v>825</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -15845,7 +15838,7 @@
         <v>825</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -15859,7 +15852,7 @@
         <v>825</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -15873,7 +15866,7 @@
         <v>825</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -15887,7 +15880,7 @@
         <v>825</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -15901,7 +15894,7 @@
         <v>825</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -15915,7 +15908,7 @@
         <v>825</v>
       </c>
       <c r="D493" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -15929,7 +15922,7 @@
         <v>825</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -15943,7 +15936,7 @@
         <v>825</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -16153,7 +16146,7 @@
         <v>825</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -16181,7 +16174,7 @@
         <v>825</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -16195,7 +16188,7 @@
         <v>825</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -16223,7 +16216,7 @@
         <v>825</v>
       </c>
       <c r="D515" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -16251,7 +16244,7 @@
         <v>825</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -16265,7 +16258,7 @@
         <v>825</v>
       </c>
       <c r="D518" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -16293,7 +16286,7 @@
         <v>825</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -16321,7 +16314,7 @@
         <v>825</v>
       </c>
       <c r="D522" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -16335,7 +16328,7 @@
         <v>825</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -16363,7 +16356,7 @@
         <v>825</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -16391,7 +16384,7 @@
         <v>825</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -16405,7 +16398,7 @@
         <v>825</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -16433,7 +16426,7 @@
         <v>825</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -16461,7 +16454,7 @@
         <v>825</v>
       </c>
       <c r="D532" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -16475,7 +16468,7 @@
         <v>825</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -16503,7 +16496,7 @@
         <v>825</v>
       </c>
       <c r="D535" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -16531,7 +16524,7 @@
         <v>825</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -16545,7 +16538,7 @@
         <v>825</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -16573,7 +16566,7 @@
         <v>825</v>
       </c>
       <c r="D540" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -16601,7 +16594,7 @@
         <v>825</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -16615,7 +16608,7 @@
         <v>825</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -16643,7 +16636,7 @@
         <v>825</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -16671,7 +16664,7 @@
         <v>825</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -16685,7 +16678,7 @@
         <v>825</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -16713,7 +16706,7 @@
         <v>825</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -16741,7 +16734,7 @@
         <v>825</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -16755,7 +16748,7 @@
         <v>825</v>
       </c>
       <c r="D553" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -16783,7 +16776,7 @@
         <v>825</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -16811,7 +16804,7 @@
         <v>825</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -16825,7 +16818,7 @@
         <v>825</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -16853,7 +16846,7 @@
         <v>825</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -16881,7 +16874,7 @@
         <v>825</v>
       </c>
       <c r="D562" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -16895,7 +16888,7 @@
         <v>825</v>
       </c>
       <c r="D563" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -16923,7 +16916,7 @@
         <v>825</v>
       </c>
       <c r="D565" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -16951,7 +16944,7 @@
         <v>825</v>
       </c>
       <c r="D567" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -16965,7 +16958,7 @@
         <v>825</v>
       </c>
       <c r="D568" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -16993,7 +16986,7 @@
         <v>825</v>
       </c>
       <c r="D570" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -17021,7 +17014,7 @@
         <v>825</v>
       </c>
       <c r="D572" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -17035,7 +17028,7 @@
         <v>825</v>
       </c>
       <c r="D573" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -17063,7 +17056,7 @@
         <v>825</v>
       </c>
       <c r="D575" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -17091,7 +17084,7 @@
         <v>825</v>
       </c>
       <c r="D577" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -17105,7 +17098,7 @@
         <v>825</v>
       </c>
       <c r="D578" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -17133,7 +17126,7 @@
         <v>825</v>
       </c>
       <c r="D580" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -17161,7 +17154,7 @@
         <v>825</v>
       </c>
       <c r="D582" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -17175,7 +17168,7 @@
         <v>825</v>
       </c>
       <c r="D583" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -17203,7 +17196,7 @@
         <v>825</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -17231,7 +17224,7 @@
         <v>825</v>
       </c>
       <c r="D587" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -17245,7 +17238,7 @@
         <v>825</v>
       </c>
       <c r="D588" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -17273,7 +17266,7 @@
         <v>825</v>
       </c>
       <c r="D590" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -17301,7 +17294,7 @@
         <v>825</v>
       </c>
       <c r="D592" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -17315,7 +17308,7 @@
         <v>825</v>
       </c>
       <c r="D593" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -17343,7 +17336,7 @@
         <v>825</v>
       </c>
       <c r="D595" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -17371,7 +17364,7 @@
         <v>825</v>
       </c>
       <c r="D597" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -17385,7 +17378,7 @@
         <v>825</v>
       </c>
       <c r="D598" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -17413,7 +17406,7 @@
         <v>825</v>
       </c>
       <c r="D600" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -17441,7 +17434,7 @@
         <v>825</v>
       </c>
       <c r="D602" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -17455,7 +17448,7 @@
         <v>825</v>
       </c>
       <c r="D603" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -17483,7 +17476,7 @@
         <v>825</v>
       </c>
       <c r="D605" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -17511,7 +17504,7 @@
         <v>825</v>
       </c>
       <c r="D607" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -17525,7 +17518,7 @@
         <v>825</v>
       </c>
       <c r="D608" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -17553,7 +17546,7 @@
         <v>825</v>
       </c>
       <c r="D610" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -17581,7 +17574,7 @@
         <v>825</v>
       </c>
       <c r="D612" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -17595,7 +17588,7 @@
         <v>825</v>
       </c>
       <c r="D613" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -17623,7 +17616,7 @@
         <v>825</v>
       </c>
       <c r="D615" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -17651,7 +17644,7 @@
         <v>825</v>
       </c>
       <c r="D617" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -17665,7 +17658,7 @@
         <v>825</v>
       </c>
       <c r="D618" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -17693,7 +17686,7 @@
         <v>825</v>
       </c>
       <c r="D620" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -17721,7 +17714,7 @@
         <v>825</v>
       </c>
       <c r="D622" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -17735,7 +17728,7 @@
         <v>825</v>
       </c>
       <c r="D623" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -17763,7 +17756,7 @@
         <v>825</v>
       </c>
       <c r="D625" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -17791,7 +17784,7 @@
         <v>825</v>
       </c>
       <c r="D627" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -17805,7 +17798,7 @@
         <v>825</v>
       </c>
       <c r="D628" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -17833,7 +17826,7 @@
         <v>825</v>
       </c>
       <c r="D630" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -17861,7 +17854,7 @@
         <v>825</v>
       </c>
       <c r="D632" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -17875,7 +17868,7 @@
         <v>825</v>
       </c>
       <c r="D633" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -17903,7 +17896,7 @@
         <v>825</v>
       </c>
       <c r="D635" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -17931,7 +17924,7 @@
         <v>825</v>
       </c>
       <c r="D637" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -17945,7 +17938,7 @@
         <v>825</v>
       </c>
       <c r="D638" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -17973,7 +17966,7 @@
         <v>825</v>
       </c>
       <c r="D640" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -18001,7 +17994,7 @@
         <v>825</v>
       </c>
       <c r="D642" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -18015,7 +18008,7 @@
         <v>825</v>
       </c>
       <c r="D643" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -18043,7 +18036,7 @@
         <v>825</v>
       </c>
       <c r="D645" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -18071,7 +18064,7 @@
         <v>825</v>
       </c>
       <c r="D647" s="3" t="s">
-        <v>2838</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -18085,7 +18078,7 @@
         <v>825</v>
       </c>
       <c r="D648" s="3" t="s">
-        <v>2838</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -18113,7 +18106,7 @@
         <v>825</v>
       </c>
       <c r="D650" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -18141,7 +18134,7 @@
         <v>825</v>
       </c>
       <c r="D652" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -18155,7 +18148,7 @@
         <v>825</v>
       </c>
       <c r="D653" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -18183,7 +18176,7 @@
         <v>825</v>
       </c>
       <c r="D655" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -18211,7 +18204,7 @@
         <v>825</v>
       </c>
       <c r="D657" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -18225,7 +18218,7 @@
         <v>825</v>
       </c>
       <c r="D658" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -18253,7 +18246,7 @@
         <v>825</v>
       </c>
       <c r="D660" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -18309,7 +18302,7 @@
         <v>825</v>
       </c>
       <c r="D664" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -18323,7 +18316,7 @@
         <v>825</v>
       </c>
       <c r="D665" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="666" spans="1:4">
@@ -18351,7 +18344,7 @@
         <v>825</v>
       </c>
       <c r="D667" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="668" spans="1:4">
@@ -18407,7 +18400,7 @@
         <v>825</v>
       </c>
       <c r="D671" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -18421,7 +18414,7 @@
         <v>825</v>
       </c>
       <c r="D672" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -18449,7 +18442,7 @@
         <v>825</v>
       </c>
       <c r="D674" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -18505,7 +18498,7 @@
         <v>825</v>
       </c>
       <c r="D678" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -18519,7 +18512,7 @@
         <v>825</v>
       </c>
       <c r="D679" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -18547,7 +18540,7 @@
         <v>825</v>
       </c>
       <c r="D681" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -18603,7 +18596,7 @@
         <v>825</v>
       </c>
       <c r="D685" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -18617,7 +18610,7 @@
         <v>825</v>
       </c>
       <c r="D686" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -18645,7 +18638,7 @@
         <v>825</v>
       </c>
       <c r="D688" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -18701,7 +18694,7 @@
         <v>825</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -18715,7 +18708,7 @@
         <v>825</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -18743,7 +18736,7 @@
         <v>825</v>
       </c>
       <c r="D695" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -18799,7 +18792,7 @@
         <v>825</v>
       </c>
       <c r="D699" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -18813,7 +18806,7 @@
         <v>825</v>
       </c>
       <c r="D700" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -18841,7 +18834,7 @@
         <v>825</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -18897,7 +18890,7 @@
         <v>825</v>
       </c>
       <c r="D706" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -18911,7 +18904,7 @@
         <v>825</v>
       </c>
       <c r="D707" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -18981,7 +18974,7 @@
         <v>825</v>
       </c>
       <c r="D712" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -18995,7 +18988,7 @@
         <v>825</v>
       </c>
       <c r="D713" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -19009,7 +19002,7 @@
         <v>825</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -19023,7 +19016,7 @@
         <v>825</v>
       </c>
       <c r="D715" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -19051,7 +19044,7 @@
         <v>825</v>
       </c>
       <c r="D717" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -19065,7 +19058,7 @@
         <v>825</v>
       </c>
       <c r="D718" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -19079,7 +19072,7 @@
         <v>825</v>
       </c>
       <c r="D719" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -19093,7 +19086,7 @@
         <v>825</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -19107,7 +19100,7 @@
         <v>825</v>
       </c>
       <c r="D721" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -19121,7 +19114,7 @@
         <v>825</v>
       </c>
       <c r="D722" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -19135,7 +19128,7 @@
         <v>825</v>
       </c>
       <c r="D723" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -19149,7 +19142,7 @@
         <v>825</v>
       </c>
       <c r="D724" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -19163,7 +19156,7 @@
         <v>825</v>
       </c>
       <c r="D725" s="3" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -19373,7 +19366,7 @@
         <v>825</v>
       </c>
       <c r="D740" s="3" t="s">
-        <v>2831</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -19401,7 +19394,7 @@
         <v>1516</v>
       </c>
       <c r="D742" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -19457,7 +19450,7 @@
         <v>1516</v>
       </c>
       <c r="D746" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="747" spans="1:4">
@@ -19485,7 +19478,7 @@
         <v>1516</v>
       </c>
       <c r="D748" s="3" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="749" spans="1:4">
@@ -19499,7 +19492,7 @@
         <v>1516</v>
       </c>
       <c r="D749" s="3" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="750" spans="1:4">
@@ -19513,7 +19506,7 @@
         <v>1516</v>
       </c>
       <c r="D750" s="3" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="751" spans="1:4">
@@ -21053,7 +21046,7 @@
         <v>1516</v>
       </c>
       <c r="D860" s="3" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="861" spans="1:4">
@@ -21081,7 +21074,7 @@
         <v>1516</v>
       </c>
       <c r="D862" s="3" t="s">
-        <v>2830</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="863" spans="1:4">
@@ -21823,7 +21816,7 @@
         <v>1516</v>
       </c>
       <c r="D915" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="916" spans="1:4">
@@ -21837,7 +21830,7 @@
         <v>1516</v>
       </c>
       <c r="D916" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="917" spans="1:4">
@@ -21949,7 +21942,7 @@
         <v>1516</v>
       </c>
       <c r="D924" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="925" spans="1:4">
@@ -21963,7 +21956,7 @@
         <v>1516</v>
       </c>
       <c r="D925" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="926" spans="1:4">
@@ -21977,7 +21970,7 @@
         <v>1516</v>
       </c>
       <c r="D926" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="927" spans="1:4">
@@ -21991,7 +21984,7 @@
         <v>1516</v>
       </c>
       <c r="D927" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="928" spans="1:4">
@@ -22005,7 +21998,7 @@
         <v>1516</v>
       </c>
       <c r="D928" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="929" spans="1:4">
@@ -22019,7 +22012,7 @@
         <v>1516</v>
       </c>
       <c r="D929" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="930" spans="1:4">
@@ -22089,7 +22082,7 @@
         <v>1516</v>
       </c>
       <c r="D934" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="935" spans="1:4">
@@ -22103,7 +22096,7 @@
         <v>1516</v>
       </c>
       <c r="D935" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="936" spans="1:4">
@@ -22215,7 +22208,7 @@
         <v>1516</v>
       </c>
       <c r="D943" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="944" spans="1:4">
@@ -22229,7 +22222,7 @@
         <v>1516</v>
       </c>
       <c r="D944" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="945" spans="1:4">
@@ -22243,7 +22236,7 @@
         <v>1516</v>
       </c>
       <c r="D945" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="946" spans="1:4">
@@ -22257,7 +22250,7 @@
         <v>1516</v>
       </c>
       <c r="D946" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="947" spans="1:4">
@@ -22271,7 +22264,7 @@
         <v>1516</v>
       </c>
       <c r="D947" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="948" spans="1:4">
@@ -22355,7 +22348,7 @@
         <v>1516</v>
       </c>
       <c r="D953" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="954" spans="1:4">
@@ -22369,7 +22362,7 @@
         <v>1516</v>
       </c>
       <c r="D954" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="955" spans="1:4">
@@ -22481,7 +22474,7 @@
         <v>1516</v>
       </c>
       <c r="D962" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="963" spans="1:4">
@@ -22495,7 +22488,7 @@
         <v>1516</v>
       </c>
       <c r="D963" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="964" spans="1:4">
@@ -22509,7 +22502,7 @@
         <v>1516</v>
       </c>
       <c r="D964" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="965" spans="1:4">
@@ -22579,7 +22572,7 @@
         <v>1516</v>
       </c>
       <c r="D969" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="970" spans="1:4">
@@ -22593,7 +22586,7 @@
         <v>1516</v>
       </c>
       <c r="D970" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="971" spans="1:4">
@@ -22705,7 +22698,7 @@
         <v>1516</v>
       </c>
       <c r="D978" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="979" spans="1:4">
@@ -22719,7 +22712,7 @@
         <v>1516</v>
       </c>
       <c r="D979" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="980" spans="1:4">
@@ -22733,7 +22726,7 @@
         <v>1516</v>
       </c>
       <c r="D980" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="981" spans="1:4">
@@ -22803,7 +22796,7 @@
         <v>1516</v>
       </c>
       <c r="D985" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="986" spans="1:4">
@@ -22817,7 +22810,7 @@
         <v>1516</v>
       </c>
       <c r="D986" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="987" spans="1:4">
@@ -22929,7 +22922,7 @@
         <v>1516</v>
       </c>
       <c r="D994" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="995" spans="1:4">
@@ -22943,7 +22936,7 @@
         <v>1516</v>
       </c>
       <c r="D995" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="996" spans="1:4">
@@ -22957,7 +22950,7 @@
         <v>1516</v>
       </c>
       <c r="D996" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="997" spans="1:4">
@@ -23027,7 +23020,7 @@
         <v>1516</v>
       </c>
       <c r="D1001" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1002" spans="1:4">
@@ -23041,7 +23034,7 @@
         <v>1516</v>
       </c>
       <c r="D1002" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1003" spans="1:4">
@@ -23153,7 +23146,7 @@
         <v>1516</v>
       </c>
       <c r="D1010" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1011" spans="1:4">
@@ -23167,7 +23160,7 @@
         <v>1516</v>
       </c>
       <c r="D1011" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1012" spans="1:4">
@@ -23181,7 +23174,7 @@
         <v>1516</v>
       </c>
       <c r="D1012" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1013" spans="1:4">
@@ -23195,7 +23188,7 @@
         <v>1516</v>
       </c>
       <c r="D1013" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1014" spans="1:4">
@@ -23265,7 +23258,7 @@
         <v>1516</v>
       </c>
       <c r="D1018" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1019" spans="1:4">
@@ -23279,7 +23272,7 @@
         <v>1516</v>
       </c>
       <c r="D1019" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1020" spans="1:4">
@@ -23391,7 +23384,7 @@
         <v>1516</v>
       </c>
       <c r="D1027" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1028" spans="1:4">
@@ -23405,7 +23398,7 @@
         <v>1516</v>
       </c>
       <c r="D1028" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1029" spans="1:4">
@@ -23419,7 +23412,7 @@
         <v>1516</v>
       </c>
       <c r="D1029" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1030" spans="1:4">
@@ -23433,7 +23426,7 @@
         <v>1516</v>
       </c>
       <c r="D1030" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1031" spans="1:4">
@@ -23503,7 +23496,7 @@
         <v>1516</v>
       </c>
       <c r="D1035" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1036" spans="1:4">
@@ -23517,7 +23510,7 @@
         <v>1516</v>
       </c>
       <c r="D1036" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1037" spans="1:4">
@@ -23629,7 +23622,7 @@
         <v>1516</v>
       </c>
       <c r="D1044" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1045" spans="1:4">
@@ -23643,7 +23636,7 @@
         <v>1516</v>
       </c>
       <c r="D1045" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1046" spans="1:4">
@@ -23657,7 +23650,7 @@
         <v>1516</v>
       </c>
       <c r="D1046" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1047" spans="1:4">
@@ -23671,7 +23664,7 @@
         <v>1516</v>
       </c>
       <c r="D1047" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1048" spans="1:4">
@@ -23741,7 +23734,7 @@
         <v>1516</v>
       </c>
       <c r="D1052" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1053" spans="1:4">
@@ -23755,7 +23748,7 @@
         <v>1516</v>
       </c>
       <c r="D1053" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1054" spans="1:4">
@@ -23867,7 +23860,7 @@
         <v>1516</v>
       </c>
       <c r="D1061" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1062" spans="1:4">
@@ -23881,7 +23874,7 @@
         <v>1516</v>
       </c>
       <c r="D1062" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1063" spans="1:4">
@@ -23895,7 +23888,7 @@
         <v>1516</v>
       </c>
       <c r="D1063" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1064" spans="1:4">
@@ -23909,7 +23902,7 @@
         <v>1516</v>
       </c>
       <c r="D1064" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1065" spans="1:4">
@@ -23979,7 +23972,7 @@
         <v>1516</v>
       </c>
       <c r="D1069" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1070" spans="1:4">
@@ -23993,7 +23986,7 @@
         <v>1516</v>
       </c>
       <c r="D1070" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1071" spans="1:4">
@@ -24105,7 +24098,7 @@
         <v>1516</v>
       </c>
       <c r="D1078" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1079" spans="1:4">
@@ -24119,7 +24112,7 @@
         <v>1516</v>
       </c>
       <c r="D1079" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1080" spans="1:4">
@@ -24133,7 +24126,7 @@
         <v>1516</v>
       </c>
       <c r="D1080" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1081" spans="1:4">
@@ -24147,7 +24140,7 @@
         <v>1516</v>
       </c>
       <c r="D1081" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1082" spans="1:4">
@@ -24217,7 +24210,7 @@
         <v>1516</v>
       </c>
       <c r="D1086" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1087" spans="1:4">
@@ -24231,7 +24224,7 @@
         <v>1516</v>
       </c>
       <c r="D1087" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1088" spans="1:4">
@@ -24343,7 +24336,7 @@
         <v>1516</v>
       </c>
       <c r="D1095" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1096" spans="1:4">
@@ -24357,7 +24350,7 @@
         <v>1516</v>
       </c>
       <c r="D1096" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1097" spans="1:4">
@@ -24371,7 +24364,7 @@
         <v>1516</v>
       </c>
       <c r="D1097" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1098" spans="1:4">
@@ -24385,7 +24378,7 @@
         <v>1516</v>
       </c>
       <c r="D1098" s="3" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="1099" spans="1:4">
@@ -24455,7 +24448,7 @@
         <v>1516</v>
       </c>
       <c r="D1103" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1104" spans="1:4">
@@ -24469,7 +24462,7 @@
         <v>1516</v>
       </c>
       <c r="D1104" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1105" spans="1:4">
@@ -24581,7 +24574,7 @@
         <v>1516</v>
       </c>
       <c r="D1112" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1113" spans="1:4">
@@ -24595,7 +24588,7 @@
         <v>1516</v>
       </c>
       <c r="D1113" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1114" spans="1:4">
@@ -24609,7 +24602,7 @@
         <v>1516</v>
       </c>
       <c r="D1114" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1115" spans="1:4">
@@ -24679,7 +24672,7 @@
         <v>1516</v>
       </c>
       <c r="D1119" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1120" spans="1:4">
@@ -24693,7 +24686,7 @@
         <v>1516</v>
       </c>
       <c r="D1120" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1121" spans="1:4">
@@ -24805,7 +24798,7 @@
         <v>1516</v>
       </c>
       <c r="D1128" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1129" spans="1:4">
@@ -24819,7 +24812,7 @@
         <v>1516</v>
       </c>
       <c r="D1129" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1130" spans="1:4">
@@ -24833,7 +24826,7 @@
         <v>1516</v>
       </c>
       <c r="D1130" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1131" spans="1:4">
@@ -24847,7 +24840,7 @@
         <v>1516</v>
       </c>
       <c r="D1131" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1132" spans="1:4">
@@ -24931,7 +24924,7 @@
         <v>1516</v>
       </c>
       <c r="D1137" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1138" spans="1:4">
@@ -24945,7 +24938,7 @@
         <v>1516</v>
       </c>
       <c r="D1138" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1139" spans="1:4">
@@ -25057,7 +25050,7 @@
         <v>1516</v>
       </c>
       <c r="D1146" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1147" spans="1:4">
@@ -25071,7 +25064,7 @@
         <v>1516</v>
       </c>
       <c r="D1147" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1148" spans="1:4">
@@ -25085,7 +25078,7 @@
         <v>1516</v>
       </c>
       <c r="D1148" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1149" spans="1:4">
@@ -25099,7 +25092,7 @@
         <v>1516</v>
       </c>
       <c r="D1149" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1150" spans="1:4">
@@ -25183,7 +25176,7 @@
         <v>1516</v>
       </c>
       <c r="D1155" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1156" spans="1:4">
@@ -25197,7 +25190,7 @@
         <v>1516</v>
       </c>
       <c r="D1156" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1157" spans="1:4">
@@ -25309,7 +25302,7 @@
         <v>1516</v>
       </c>
       <c r="D1164" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1165" spans="1:4">
@@ -25323,7 +25316,7 @@
         <v>1516</v>
       </c>
       <c r="D1165" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1166" spans="1:4">
@@ -25337,7 +25330,7 @@
         <v>1516</v>
       </c>
       <c r="D1166" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1167" spans="1:4">
@@ -25407,7 +25400,7 @@
         <v>1516</v>
       </c>
       <c r="D1171" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1172" spans="1:4">
@@ -25421,7 +25414,7 @@
         <v>1516</v>
       </c>
       <c r="D1172" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1173" spans="1:4">
@@ -25533,7 +25526,7 @@
         <v>1516</v>
       </c>
       <c r="D1180" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1181" spans="1:4">
@@ -25547,7 +25540,7 @@
         <v>1516</v>
       </c>
       <c r="D1181" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1182" spans="1:4">
@@ -25561,7 +25554,7 @@
         <v>1516</v>
       </c>
       <c r="D1182" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1183" spans="1:4">
@@ -25631,7 +25624,7 @@
         <v>1516</v>
       </c>
       <c r="D1187" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1188" spans="1:4">
@@ -25645,7 +25638,7 @@
         <v>1516</v>
       </c>
       <c r="D1188" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1189" spans="1:4">
@@ -25687,7 +25680,7 @@
         <v>1516</v>
       </c>
       <c r="D1191" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1192" spans="1:4">
@@ -25701,7 +25694,7 @@
         <v>1516</v>
       </c>
       <c r="D1192" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1193" spans="1:4">
@@ -25715,7 +25708,7 @@
         <v>1516</v>
       </c>
       <c r="D1193" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1194" spans="1:4">
@@ -25799,7 +25792,7 @@
         <v>1516</v>
       </c>
       <c r="D1199" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1200" spans="1:4">
@@ -25813,7 +25806,7 @@
         <v>1516</v>
       </c>
       <c r="D1200" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1201" spans="1:4">
@@ -25855,7 +25848,7 @@
         <v>1516</v>
       </c>
       <c r="D1203" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1204" spans="1:4">
@@ -25869,7 +25862,7 @@
         <v>1516</v>
       </c>
       <c r="D1204" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1205" spans="1:4">
@@ -25939,7 +25932,7 @@
         <v>1516</v>
       </c>
       <c r="D1209" s="3" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="1210" spans="1:4">
@@ -25953,7 +25946,7 @@
         <v>1516</v>
       </c>
       <c r="D1210" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1211" spans="1:4">
@@ -25995,7 +25988,7 @@
         <v>1516</v>
       </c>
       <c r="D1213" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1214" spans="1:4">
@@ -26009,7 +26002,7 @@
         <v>1516</v>
       </c>
       <c r="D1214" s="3" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1215" spans="1:4">
@@ -26023,7 +26016,7 @@
         <v>1516</v>
       </c>
       <c r="D1215" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1216" spans="1:4">
@@ -26037,7 +26030,7 @@
         <v>1516</v>
       </c>
       <c r="D1216" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1217" spans="1:4">
@@ -26051,7 +26044,7 @@
         <v>1516</v>
       </c>
       <c r="D1217" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1218" spans="1:4">
@@ -26065,7 +26058,7 @@
         <v>1516</v>
       </c>
       <c r="D1218" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1219" spans="1:4">
@@ -26079,7 +26072,7 @@
         <v>1516</v>
       </c>
       <c r="D1219" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1220" spans="1:4">
@@ -26093,7 +26086,7 @@
         <v>1516</v>
       </c>
       <c r="D1220" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1221" spans="1:4">
@@ -26149,7 +26142,7 @@
         <v>1516</v>
       </c>
       <c r="D1224" s="3" t="s">
-        <v>2831</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="1225" spans="1:4">
@@ -26163,7 +26156,7 @@
         <v>1516</v>
       </c>
       <c r="D1225" s="3" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="1226" spans="1:4">
@@ -26173,7 +26166,9 @@
       <c r="B1226" s="2" t="s">
         <v>2486</v>
       </c>
-      <c r="C1226" s="3"/>
+      <c r="C1226" s="3" t="s">
+        <v>2843</v>
+      </c>
       <c r="D1226" s="3" t="s">
         <v>45</v>
       </c>
@@ -26189,7 +26184,7 @@
         <v>363</v>
       </c>
       <c r="D1227" s="3" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1228" spans="1:4">
@@ -26200,21 +26195,21 @@
         <v>2490</v>
       </c>
       <c r="C1228" s="3" t="s">
-        <v>2491</v>
+        <v>363</v>
       </c>
       <c r="D1228" s="3" t="s">
-        <v>2840</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1229" spans="1:4">
       <c r="A1229" s="2" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B1229" s="2" t="s">
         <v>2492</v>
       </c>
-      <c r="B1229" s="2" t="s">
-        <v>2493</v>
-      </c>
       <c r="C1229" s="3" t="s">
-        <v>2494</v>
+        <v>363</v>
       </c>
       <c r="D1229" s="3" t="s">
         <v>238</v>
@@ -26222,13 +26217,13 @@
     </row>
     <row r="1230" spans="1:4">
       <c r="A1230" s="2" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="B1230" s="2" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="C1230" s="3" t="s">
-        <v>2497</v>
+        <v>363</v>
       </c>
       <c r="D1230" s="3" t="s">
         <v>161</v>
@@ -26236,38 +26231,38 @@
     </row>
     <row r="1231" spans="1:4">
       <c r="A1231" s="2" t="s">
-        <v>2498</v>
+        <v>2495</v>
       </c>
       <c r="B1231" s="2" t="s">
-        <v>2499</v>
+        <v>2496</v>
       </c>
       <c r="C1231" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1231" s="3" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1232" spans="1:4">
       <c r="A1232" s="2" t="s">
-        <v>2500</v>
+        <v>2497</v>
       </c>
       <c r="B1232" s="2" t="s">
-        <v>2501</v>
+        <v>2498</v>
       </c>
       <c r="C1232" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1232" s="3" t="s">
-        <v>2840</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1233" spans="1:4">
       <c r="A1233" s="2" t="s">
-        <v>2502</v>
+        <v>2499</v>
       </c>
       <c r="B1233" s="2" t="s">
-        <v>2503</v>
+        <v>2500</v>
       </c>
       <c r="C1233" s="3" t="s">
         <v>825</v>
@@ -26278,38 +26273,38 @@
     </row>
     <row r="1234" spans="1:4">
       <c r="A1234" s="2" t="s">
-        <v>2504</v>
+        <v>2501</v>
       </c>
       <c r="B1234" s="2" t="s">
-        <v>2505</v>
+        <v>2502</v>
       </c>
       <c r="C1234" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1234" s="3" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1235" spans="1:4">
       <c r="A1235" s="2" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="B1235" s="2" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
       <c r="C1235" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1235" s="3" t="s">
-        <v>2840</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1236" spans="1:4">
       <c r="A1236" s="2" t="s">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="B1236" s="2" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
       <c r="C1236" s="3" t="s">
         <v>1516</v>
@@ -26320,273 +26315,279 @@
     </row>
     <row r="1237" spans="1:4">
       <c r="A1237" s="2" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="B1237" s="2" t="s">
-        <v>2511</v>
-      </c>
-      <c r="C1237" s="3"/>
+        <v>2508</v>
+      </c>
+      <c r="C1237" s="3" t="s">
+        <v>2843</v>
+      </c>
       <c r="D1237" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="1238" spans="1:4">
       <c r="A1238" s="2" t="s">
-        <v>2512</v>
+        <v>2509</v>
       </c>
       <c r="B1238" s="2" t="s">
-        <v>2513</v>
-      </c>
-      <c r="C1238" s="3"/>
+        <v>2510</v>
+      </c>
+      <c r="C1238" s="3" t="s">
+        <v>2843</v>
+      </c>
       <c r="D1238" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1239" spans="1:4">
       <c r="A1239" s="2" t="s">
-        <v>2514</v>
+        <v>2511</v>
       </c>
       <c r="B1239" s="2" t="s">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="C1239" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1239" s="3" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1240" spans="1:4">
       <c r="A1240" s="2" t="s">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="B1240" s="2" t="s">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="C1240" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1240" s="3" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="1241" spans="1:4">
       <c r="A1241" s="2" t="s">
-        <v>2518</v>
+        <v>2515</v>
       </c>
       <c r="B1241" s="2" t="s">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="C1241" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1241" s="3" t="s">
-        <v>2842</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="1242" spans="1:4">
       <c r="A1242" s="2" t="s">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="B1242" s="2" t="s">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="C1242" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1242" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1243" spans="1:4">
       <c r="A1243" s="2" t="s">
-        <v>2522</v>
+        <v>2519</v>
       </c>
       <c r="B1243" s="2" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="C1243" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1243" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1244" spans="1:4">
       <c r="A1244" s="2" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="B1244" s="2" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="C1244" s="3" t="s">
         <v>825</v>
       </c>
       <c r="D1244" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1245" spans="1:4">
       <c r="A1245" s="2" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="B1245" s="2" t="s">
-        <v>2527</v>
-      </c>
-      <c r="C1245" s="3"/>
+        <v>2524</v>
+      </c>
+      <c r="C1245" s="3" t="s">
+        <v>2843</v>
+      </c>
       <c r="D1245" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1246" spans="1:4">
       <c r="A1246" s="2" t="s">
-        <v>2528</v>
+        <v>2525</v>
       </c>
       <c r="B1246" s="2" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="C1246" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1246" s="3" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1247" spans="1:4">
       <c r="A1247" s="2" t="s">
-        <v>2530</v>
+        <v>2527</v>
       </c>
       <c r="B1247" s="2" t="s">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="C1247" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1247" s="3" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="1248" spans="1:4">
       <c r="A1248" s="2" t="s">
-        <v>2533</v>
+        <v>2530</v>
       </c>
       <c r="B1248" s="2" t="s">
-        <v>2534</v>
+        <v>2531</v>
       </c>
       <c r="C1248" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1248" s="3" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1249" spans="1:4">
       <c r="A1249" s="2" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="B1249" s="2" t="s">
-        <v>2536</v>
+        <v>2533</v>
       </c>
       <c r="C1249" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1249" s="3" t="s">
-        <v>2842</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="1250" spans="1:4">
       <c r="A1250" s="2" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="B1250" s="2" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="C1250" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1250" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1251" spans="1:4">
       <c r="A1251" s="2" t="s">
-        <v>2539</v>
+        <v>2536</v>
       </c>
       <c r="B1251" s="2" t="s">
-        <v>2540</v>
+        <v>2537</v>
       </c>
       <c r="C1251" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1251" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1252" spans="1:4">
       <c r="A1252" s="2" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
       <c r="B1252" s="2" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
       <c r="C1252" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1252" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1253" spans="1:4">
       <c r="A1253" s="2" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
       <c r="B1253" s="2" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="C1253" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1253" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1254" spans="1:4">
       <c r="A1254" s="2" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="B1254" s="2" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="C1254" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1254" s="3" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1255" spans="1:4">
       <c r="A1255" s="2" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="B1255" s="2" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="C1255" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="D1255" s="3" t="s">
-        <v>2842</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="1256" spans="1:4">
       <c r="A1256" s="2" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="B1256" s="2" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="C1256" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1256" s="3" t="s">
         <v>45</v>
@@ -26594,13 +26595,13 @@
     </row>
     <row r="1257" spans="1:4">
       <c r="A1257" s="2" t="s">
-        <v>2552</v>
+        <v>2549</v>
       </c>
       <c r="B1257" s="2" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="C1257" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1257" s="3" t="s">
         <v>38</v>
@@ -26608,13 +26609,13 @@
     </row>
     <row r="1258" spans="1:4">
       <c r="A1258" s="2" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="B1258" s="2" t="s">
-        <v>2555</v>
+        <v>2552</v>
       </c>
       <c r="C1258" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1258" s="3" t="s">
         <v>38</v>
@@ -26622,13 +26623,13 @@
     </row>
     <row r="1259" spans="1:4">
       <c r="A1259" s="2" t="s">
-        <v>2556</v>
+        <v>2553</v>
       </c>
       <c r="B1259" s="2" t="s">
-        <v>2557</v>
+        <v>2554</v>
       </c>
       <c r="C1259" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1259" s="3" t="s">
         <v>58</v>
@@ -26636,13 +26637,13 @@
     </row>
     <row r="1260" spans="1:4">
       <c r="A1260" s="2" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="B1260" s="2" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="C1260" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1260" s="3" t="s">
         <v>58</v>
@@ -26650,13 +26651,13 @@
     </row>
     <row r="1261" spans="1:4">
       <c r="A1261" s="2" t="s">
-        <v>2560</v>
+        <v>2557</v>
       </c>
       <c r="B1261" s="2" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="C1261" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1261" s="3" t="s">
         <v>58</v>
@@ -26664,27 +26665,27 @@
     </row>
     <row r="1262" spans="1:4">
       <c r="A1262" s="2" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="B1262" s="2" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="C1262" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1262" s="3" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="1263" spans="1:4">
       <c r="A1263" s="2" t="s">
-        <v>2564</v>
+        <v>2561</v>
       </c>
       <c r="B1263" s="2" t="s">
-        <v>2565</v>
+        <v>2562</v>
       </c>
       <c r="C1263" s="3" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="D1263" s="3" t="s">
         <v>38</v>
@@ -26692,13 +26693,13 @@
     </row>
     <row r="1264" spans="1:4">
       <c r="A1264" s="2" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
       <c r="B1264" s="2" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
       <c r="C1264" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1264" s="3" t="s">
         <v>45</v>
@@ -26706,13 +26707,13 @@
     </row>
     <row r="1265" spans="1:4">
       <c r="A1265" s="2" t="s">
-        <v>2569</v>
+        <v>2566</v>
       </c>
       <c r="B1265" s="2" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
       <c r="C1265" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1265" s="3" t="s">
         <v>38</v>
@@ -26720,13 +26721,13 @@
     </row>
     <row r="1266" spans="1:4">
       <c r="A1266" s="2" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="B1266" s="2" t="s">
-        <v>2572</v>
+        <v>2569</v>
       </c>
       <c r="C1266" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1266" s="3" t="s">
         <v>38</v>
@@ -26734,13 +26735,13 @@
     </row>
     <row r="1267" spans="1:4">
       <c r="A1267" s="2" t="s">
-        <v>2573</v>
+        <v>2570</v>
       </c>
       <c r="B1267" s="2" t="s">
-        <v>2574</v>
+        <v>2571</v>
       </c>
       <c r="C1267" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1267" s="3" t="s">
         <v>471</v>
@@ -26748,13 +26749,13 @@
     </row>
     <row r="1268" spans="1:4">
       <c r="A1268" s="2" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
       <c r="B1268" s="2" t="s">
-        <v>2576</v>
+        <v>2573</v>
       </c>
       <c r="C1268" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1268" s="3" t="s">
         <v>471</v>
@@ -26762,13 +26763,13 @@
     </row>
     <row r="1269" spans="1:4">
       <c r="A1269" s="2" t="s">
-        <v>2577</v>
+        <v>2574</v>
       </c>
       <c r="B1269" s="2" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
       <c r="C1269" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1269" s="3" t="s">
         <v>58</v>
@@ -26776,13 +26777,13 @@
     </row>
     <row r="1270" spans="1:4">
       <c r="A1270" s="2" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="B1270" s="2" t="s">
-        <v>2580</v>
+        <v>2577</v>
       </c>
       <c r="C1270" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1270" s="3" t="s">
         <v>58</v>
@@ -26790,13 +26791,13 @@
     </row>
     <row r="1271" spans="1:4">
       <c r="A1271" s="2" t="s">
-        <v>2581</v>
+        <v>2578</v>
       </c>
       <c r="B1271" s="2" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="C1271" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1271" s="3" t="s">
         <v>58</v>
@@ -26804,13 +26805,13 @@
     </row>
     <row r="1272" spans="1:4">
       <c r="A1272" s="2" t="s">
-        <v>2583</v>
+        <v>2580</v>
       </c>
       <c r="B1272" s="2" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="C1272" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1272" s="3" t="s">
         <v>58</v>
@@ -26818,13 +26819,13 @@
     </row>
     <row r="1273" spans="1:4">
       <c r="A1273" s="2" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="B1273" s="2" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="C1273" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1273" s="3" t="s">
         <v>58</v>
@@ -26832,13 +26833,13 @@
     </row>
     <row r="1274" spans="1:4">
       <c r="A1274" s="2" t="s">
-        <v>2587</v>
+        <v>2584</v>
       </c>
       <c r="B1274" s="2" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="C1274" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1274" s="3" t="s">
         <v>58</v>
@@ -26846,13 +26847,13 @@
     </row>
     <row r="1275" spans="1:4">
       <c r="A1275" s="2" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="B1275" s="2" t="s">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="C1275" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1275" s="3" t="s">
         <v>58</v>
@@ -26860,13 +26861,13 @@
     </row>
     <row r="1276" spans="1:4">
       <c r="A1276" s="2" t="s">
-        <v>2591</v>
+        <v>2588</v>
       </c>
       <c r="B1276" s="2" t="s">
-        <v>2592</v>
+        <v>2589</v>
       </c>
       <c r="C1276" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1276" s="3" t="s">
         <v>58</v>
@@ -26874,27 +26875,27 @@
     </row>
     <row r="1277" spans="1:4">
       <c r="A1277" s="2" t="s">
-        <v>2593</v>
+        <v>2590</v>
       </c>
       <c r="B1277" s="2" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="C1277" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1277" s="3" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="1278" spans="1:4">
       <c r="A1278" s="2" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="B1278" s="2" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="C1278" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1278" s="3" t="s">
         <v>8</v>
@@ -26902,13 +26903,13 @@
     </row>
     <row r="1279" spans="1:4">
       <c r="A1279" s="2" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="B1279" s="2" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C1279" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1279" s="3" t="s">
         <v>238</v>
@@ -26916,13 +26917,13 @@
     </row>
     <row r="1280" spans="1:4">
       <c r="A1280" s="2" t="s">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="B1280" s="2" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="C1280" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1280" s="3" t="s">
         <v>238</v>
@@ -26930,13 +26931,13 @@
     </row>
     <row r="1281" spans="1:4">
       <c r="A1281" s="2" t="s">
-        <v>2601</v>
+        <v>2598</v>
       </c>
       <c r="B1281" s="2" t="s">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="C1281" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1281" s="3" t="s">
         <v>238</v>
@@ -26944,13 +26945,13 @@
     </row>
     <row r="1282" spans="1:4">
       <c r="A1282" s="2" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="B1282" s="2" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="C1282" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1282" s="3" t="s">
         <v>238</v>
@@ -26958,13 +26959,13 @@
     </row>
     <row r="1283" spans="1:4">
       <c r="A1283" s="2" t="s">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="B1283" s="2" t="s">
-        <v>2606</v>
+        <v>2603</v>
       </c>
       <c r="C1283" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1283" s="3" t="s">
         <v>161</v>
@@ -26972,27 +26973,27 @@
     </row>
     <row r="1284" spans="1:4">
       <c r="A1284" s="2" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="B1284" s="2" t="s">
-        <v>2608</v>
+        <v>2605</v>
       </c>
       <c r="C1284" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1284" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1285" spans="1:4">
       <c r="A1285" s="2" t="s">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="B1285" s="2" t="s">
-        <v>2610</v>
+        <v>2607</v>
       </c>
       <c r="C1285" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1285" s="3" t="s">
         <v>38</v>
@@ -27000,13 +27001,13 @@
     </row>
     <row r="1286" spans="1:4">
       <c r="A1286" s="2" t="s">
-        <v>2611</v>
+        <v>2608</v>
       </c>
       <c r="B1286" s="2" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="C1286" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1286" s="3" t="s">
         <v>238</v>
@@ -27014,27 +27015,27 @@
     </row>
     <row r="1287" spans="1:4">
       <c r="A1287" s="2" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="B1287" s="2" t="s">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="C1287" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1287" s="3" t="s">
-        <v>2844</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="1288" spans="1:4">
       <c r="A1288" s="2" t="s">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="B1288" s="2" t="s">
-        <v>2616</v>
+        <v>2613</v>
       </c>
       <c r="C1288" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1288" s="3" t="s">
         <v>8</v>
@@ -27042,27 +27043,27 @@
     </row>
     <row r="1289" spans="1:4">
       <c r="A1289" s="2" t="s">
-        <v>2617</v>
+        <v>2614</v>
       </c>
       <c r="B1289" s="2" t="s">
-        <v>2618</v>
+        <v>2615</v>
       </c>
       <c r="C1289" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1289" s="3" t="s">
-        <v>2844</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="1290" spans="1:4">
       <c r="A1290" s="2" t="s">
-        <v>2619</v>
+        <v>2616</v>
       </c>
       <c r="B1290" s="2" t="s">
-        <v>2620</v>
+        <v>2617</v>
       </c>
       <c r="C1290" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1290" s="3" t="s">
         <v>58</v>
@@ -27070,13 +27071,13 @@
     </row>
     <row r="1291" spans="1:4">
       <c r="A1291" s="2" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="B1291" s="2" t="s">
-        <v>2622</v>
+        <v>2619</v>
       </c>
       <c r="C1291" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1291" s="3" t="s">
         <v>58</v>
@@ -27084,13 +27085,13 @@
     </row>
     <row r="1292" spans="1:4">
       <c r="A1292" s="2" t="s">
-        <v>2623</v>
+        <v>2620</v>
       </c>
       <c r="B1292" s="2" t="s">
-        <v>2624</v>
+        <v>2621</v>
       </c>
       <c r="C1292" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1292" s="3" t="s">
         <v>58</v>
@@ -27098,27 +27099,27 @@
     </row>
     <row r="1293" spans="1:4">
       <c r="A1293" s="2" t="s">
-        <v>2625</v>
+        <v>2622</v>
       </c>
       <c r="B1293" s="2" t="s">
-        <v>2626</v>
+        <v>2623</v>
       </c>
       <c r="C1293" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1293" s="3" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="1294" spans="1:4">
       <c r="A1294" s="2" t="s">
-        <v>2627</v>
+        <v>2624</v>
       </c>
       <c r="B1294" s="2" t="s">
-        <v>2628</v>
+        <v>2625</v>
       </c>
       <c r="C1294" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1294" s="3" t="s">
         <v>813</v>
@@ -27126,13 +27127,13 @@
     </row>
     <row r="1295" spans="1:4">
       <c r="A1295" s="2" t="s">
-        <v>2629</v>
+        <v>2626</v>
       </c>
       <c r="B1295" s="2" t="s">
-        <v>2630</v>
+        <v>2627</v>
       </c>
       <c r="C1295" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1295" s="3" t="s">
         <v>813</v>
@@ -27140,13 +27141,13 @@
     </row>
     <row r="1296" spans="1:4">
       <c r="A1296" s="2" t="s">
-        <v>2631</v>
+        <v>2628</v>
       </c>
       <c r="B1296" s="2" t="s">
-        <v>2632</v>
+        <v>2629</v>
       </c>
       <c r="C1296" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1296" s="3" t="s">
         <v>813</v>
@@ -27154,13 +27155,13 @@
     </row>
     <row r="1297" spans="1:4">
       <c r="A1297" s="2" t="s">
-        <v>2633</v>
+        <v>2630</v>
       </c>
       <c r="B1297" s="2" t="s">
-        <v>2634</v>
+        <v>2631</v>
       </c>
       <c r="C1297" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1297" s="3" t="s">
         <v>58</v>
@@ -27168,13 +27169,13 @@
     </row>
     <row r="1298" spans="1:4">
       <c r="A1298" s="2" t="s">
-        <v>2635</v>
+        <v>2632</v>
       </c>
       <c r="B1298" s="2" t="s">
-        <v>2636</v>
+        <v>2633</v>
       </c>
       <c r="C1298" s="3" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="D1298" s="3" t="s">
         <v>292</v>
@@ -27182,13 +27183,13 @@
     </row>
     <row r="1299" spans="1:4">
       <c r="A1299" s="2" t="s">
-        <v>2637</v>
+        <v>2634</v>
       </c>
       <c r="B1299" s="2" t="s">
-        <v>2638</v>
+        <v>2635</v>
       </c>
       <c r="C1299" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1299" s="3" t="s">
         <v>45</v>
@@ -27196,13 +27197,13 @@
     </row>
     <row r="1300" spans="1:4">
       <c r="A1300" s="2" t="s">
-        <v>2640</v>
+        <v>2637</v>
       </c>
       <c r="B1300" s="2" t="s">
-        <v>2641</v>
+        <v>2638</v>
       </c>
       <c r="C1300" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1300" s="3" t="s">
         <v>8</v>
@@ -27210,13 +27211,13 @@
     </row>
     <row r="1301" spans="1:4">
       <c r="A1301" s="2" t="s">
-        <v>2642</v>
+        <v>2639</v>
       </c>
       <c r="B1301" s="2" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1301" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1301" s="3" t="s">
         <v>233</v>
@@ -27224,13 +27225,13 @@
     </row>
     <row r="1302" spans="1:4">
       <c r="A1302" s="2" t="s">
-        <v>2644</v>
+        <v>2641</v>
       </c>
       <c r="B1302" s="2" t="s">
-        <v>2645</v>
+        <v>2642</v>
       </c>
       <c r="C1302" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1302" s="3" t="s">
         <v>238</v>
@@ -27238,13 +27239,13 @@
     </row>
     <row r="1303" spans="1:4">
       <c r="A1303" s="2" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="B1303" s="2" t="s">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="C1303" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1303" s="3" t="s">
         <v>58</v>
@@ -27252,13 +27253,13 @@
     </row>
     <row r="1304" spans="1:4">
       <c r="A1304" s="2" t="s">
-        <v>2648</v>
+        <v>2645</v>
       </c>
       <c r="B1304" s="2" t="s">
-        <v>2649</v>
+        <v>2646</v>
       </c>
       <c r="C1304" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1304" s="3" t="s">
         <v>8</v>
@@ -27266,13 +27267,13 @@
     </row>
     <row r="1305" spans="1:4">
       <c r="A1305" s="2" t="s">
-        <v>2650</v>
+        <v>2647</v>
       </c>
       <c r="B1305" s="2" t="s">
-        <v>2651</v>
+        <v>2648</v>
       </c>
       <c r="C1305" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1305" s="3" t="s">
         <v>58</v>
@@ -27280,13 +27281,13 @@
     </row>
     <row r="1306" spans="1:4">
       <c r="A1306" s="2" t="s">
-        <v>2652</v>
+        <v>2649</v>
       </c>
       <c r="B1306" s="2" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="C1306" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1306" s="3" t="s">
         <v>58</v>
@@ -27294,13 +27295,13 @@
     </row>
     <row r="1307" spans="1:4">
       <c r="A1307" s="2" t="s">
-        <v>2654</v>
+        <v>2651</v>
       </c>
       <c r="B1307" s="2" t="s">
-        <v>2655</v>
+        <v>2652</v>
       </c>
       <c r="C1307" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1307" s="3" t="s">
         <v>174</v>
@@ -27308,13 +27309,13 @@
     </row>
     <row r="1308" spans="1:4">
       <c r="A1308" s="2" t="s">
-        <v>2656</v>
+        <v>2653</v>
       </c>
       <c r="B1308" s="2" t="s">
-        <v>2657</v>
+        <v>2654</v>
       </c>
       <c r="C1308" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1308" s="3" t="s">
         <v>247</v>
@@ -27322,13 +27323,13 @@
     </row>
     <row r="1309" spans="1:4">
       <c r="A1309" s="2" t="s">
-        <v>2658</v>
+        <v>2655</v>
       </c>
       <c r="B1309" s="2" t="s">
-        <v>2659</v>
+        <v>2656</v>
       </c>
       <c r="C1309" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1309" s="3" t="s">
         <v>813</v>
@@ -27336,41 +27337,41 @@
     </row>
     <row r="1310" spans="1:4">
       <c r="A1310" s="2" t="s">
-        <v>2660</v>
+        <v>2657</v>
       </c>
       <c r="B1310" s="2" t="s">
-        <v>2661</v>
+        <v>2658</v>
       </c>
       <c r="C1310" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1310" s="3" t="s">
-        <v>2836</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="1311" spans="1:4">
       <c r="A1311" s="2" t="s">
-        <v>2662</v>
+        <v>2659</v>
       </c>
       <c r="B1311" s="2" t="s">
-        <v>2663</v>
+        <v>2660</v>
       </c>
       <c r="C1311" s="3" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="D1311" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1312" spans="1:4">
       <c r="A1312" s="2" t="s">
-        <v>2664</v>
+        <v>2661</v>
       </c>
       <c r="B1312" s="2" t="s">
-        <v>2665</v>
+        <v>2662</v>
       </c>
       <c r="C1312" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1312" s="3" t="s">
         <v>45</v>
@@ -27378,13 +27379,13 @@
     </row>
     <row r="1313" spans="1:4">
       <c r="A1313" s="2" t="s">
-        <v>2667</v>
+        <v>2664</v>
       </c>
       <c r="B1313" s="2" t="s">
-        <v>2668</v>
+        <v>2665</v>
       </c>
       <c r="C1313" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1313" s="3" t="s">
         <v>8</v>
@@ -27392,13 +27393,13 @@
     </row>
     <row r="1314" spans="1:4">
       <c r="A1314" s="2" t="s">
-        <v>2669</v>
+        <v>2666</v>
       </c>
       <c r="B1314" s="2" t="s">
-        <v>2670</v>
+        <v>2667</v>
       </c>
       <c r="C1314" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1314" s="3" t="s">
         <v>38</v>
@@ -27406,13 +27407,13 @@
     </row>
     <row r="1315" spans="1:4">
       <c r="A1315" s="2" t="s">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="B1315" s="2" t="s">
-        <v>2672</v>
+        <v>2669</v>
       </c>
       <c r="C1315" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1315" s="3" t="s">
         <v>58</v>
@@ -27420,27 +27421,27 @@
     </row>
     <row r="1316" spans="1:4">
       <c r="A1316" s="2" t="s">
-        <v>2673</v>
+        <v>2670</v>
       </c>
       <c r="B1316" s="2" t="s">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="C1316" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1316" s="3" t="s">
-        <v>2841</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="1317" spans="1:4">
       <c r="A1317" s="2" t="s">
-        <v>2675</v>
+        <v>2672</v>
       </c>
       <c r="B1317" s="2" t="s">
-        <v>2676</v>
+        <v>2673</v>
       </c>
       <c r="C1317" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1317" s="3" t="s">
         <v>38</v>
@@ -27448,13 +27449,13 @@
     </row>
     <row r="1318" spans="1:4">
       <c r="A1318" s="2" t="s">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="B1318" s="2" t="s">
-        <v>2678</v>
+        <v>2675</v>
       </c>
       <c r="C1318" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1318" s="3" t="s">
         <v>161</v>
@@ -27462,13 +27463,13 @@
     </row>
     <row r="1319" spans="1:4">
       <c r="A1319" s="2" t="s">
-        <v>2679</v>
+        <v>2676</v>
       </c>
       <c r="B1319" s="2" t="s">
-        <v>2680</v>
+        <v>2677</v>
       </c>
       <c r="C1319" s="3" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="D1319" s="3" t="s">
         <v>58</v>
@@ -27476,13 +27477,13 @@
     </row>
     <row r="1320" spans="1:4">
       <c r="A1320" s="2" t="s">
-        <v>2681</v>
+        <v>2678</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="C1320" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1320" s="3" t="s">
         <v>45</v>
@@ -27490,41 +27491,41 @@
     </row>
     <row r="1321" spans="1:4">
       <c r="A1321" s="2" t="s">
-        <v>2683</v>
+        <v>2680</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
       <c r="C1321" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1321" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1322" spans="1:4">
       <c r="A1322" s="2" t="s">
-        <v>2685</v>
+        <v>2682</v>
       </c>
       <c r="B1322" s="2" t="s">
-        <v>2686</v>
+        <v>2683</v>
       </c>
       <c r="C1322" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1322" s="3" t="s">
-        <v>2834</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="1323" spans="1:4">
       <c r="A1323" s="2" t="s">
-        <v>2687</v>
+        <v>2684</v>
       </c>
       <c r="B1323" s="2" t="s">
-        <v>2688</v>
+        <v>2685</v>
       </c>
       <c r="C1323" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1323" s="3" t="s">
         <v>58</v>
@@ -27532,27 +27533,27 @@
     </row>
     <row r="1324" spans="1:4">
       <c r="A1324" s="2" t="s">
-        <v>2689</v>
+        <v>2686</v>
       </c>
       <c r="B1324" s="2" t="s">
-        <v>2690</v>
+        <v>2687</v>
       </c>
       <c r="C1324" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1324" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1325" spans="1:4">
       <c r="A1325" s="2" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="B1325" s="2" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="C1325" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1325" s="3" t="s">
         <v>8</v>
@@ -27560,13 +27561,13 @@
     </row>
     <row r="1326" spans="1:4">
       <c r="A1326" s="2" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="B1326" s="2" t="s">
-        <v>2694</v>
+        <v>2691</v>
       </c>
       <c r="C1326" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1326" s="3" t="s">
         <v>58</v>
@@ -27574,13 +27575,13 @@
     </row>
     <row r="1327" spans="1:4">
       <c r="A1327" s="2" t="s">
-        <v>2695</v>
+        <v>2692</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>2696</v>
+        <v>2693</v>
       </c>
       <c r="C1327" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1327" s="3" t="s">
         <v>58</v>
@@ -27588,13 +27589,13 @@
     </row>
     <row r="1328" spans="1:4">
       <c r="A1328" s="2" t="s">
-        <v>2697</v>
+        <v>2694</v>
       </c>
       <c r="B1328" s="2" t="s">
-        <v>2698</v>
+        <v>2695</v>
       </c>
       <c r="C1328" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1328" s="3" t="s">
         <v>38</v>
@@ -27602,13 +27603,13 @@
     </row>
     <row r="1329" spans="1:4">
       <c r="A1329" s="2" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="C1329" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1329" s="3" t="s">
         <v>58</v>
@@ -27616,13 +27617,13 @@
     </row>
     <row r="1330" spans="1:4">
       <c r="A1330" s="2" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>2702</v>
+        <v>2699</v>
       </c>
       <c r="C1330" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1330" s="3" t="s">
         <v>58</v>
@@ -27630,167 +27631,167 @@
     </row>
     <row r="1331" spans="1:4">
       <c r="A1331" s="2" t="s">
-        <v>2703</v>
+        <v>2700</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="C1331" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1331" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1332" spans="1:4">
       <c r="A1332" s="2" t="s">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="B1332" s="2" t="s">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="C1332" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1332" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1333" spans="1:4">
       <c r="A1333" s="2" t="s">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="B1333" s="2" t="s">
-        <v>2708</v>
+        <v>2705</v>
       </c>
       <c r="C1333" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1333" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1334" spans="1:4">
       <c r="A1334" s="2" t="s">
-        <v>2709</v>
+        <v>2706</v>
       </c>
       <c r="B1334" s="2" t="s">
-        <v>2710</v>
+        <v>2707</v>
       </c>
       <c r="C1334" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1334" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1335" spans="1:4">
       <c r="A1335" s="2" t="s">
-        <v>2711</v>
+        <v>2708</v>
       </c>
       <c r="B1335" s="2" t="s">
-        <v>2712</v>
+        <v>2709</v>
       </c>
       <c r="C1335" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1335" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1336" spans="1:4">
       <c r="A1336" s="2" t="s">
-        <v>2713</v>
+        <v>2710</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>2714</v>
+        <v>2711</v>
       </c>
       <c r="C1336" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1336" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1337" spans="1:4">
       <c r="A1337" s="2" t="s">
-        <v>2715</v>
+        <v>2712</v>
       </c>
       <c r="B1337" s="2" t="s">
-        <v>2716</v>
+        <v>2713</v>
       </c>
       <c r="C1337" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1337" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1338" spans="1:4">
       <c r="A1338" s="2" t="s">
-        <v>2717</v>
+        <v>2714</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="C1338" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1338" s="3" t="s">
-        <v>2719</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="1339" spans="1:4">
       <c r="A1339" s="2" t="s">
-        <v>2720</v>
+        <v>2717</v>
       </c>
       <c r="B1339" s="2" t="s">
-        <v>2721</v>
+        <v>2718</v>
       </c>
       <c r="C1339" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1339" s="3" t="s">
-        <v>2722</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="1340" spans="1:4">
       <c r="A1340" s="2" t="s">
-        <v>2723</v>
+        <v>2720</v>
       </c>
       <c r="B1340" s="2" t="s">
-        <v>2724</v>
+        <v>2721</v>
       </c>
       <c r="C1340" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1340" s="3" t="s">
-        <v>2832</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="1341" spans="1:4">
       <c r="A1341" s="2" t="s">
-        <v>2725</v>
+        <v>2722</v>
       </c>
       <c r="B1341" s="2" t="s">
-        <v>2726</v>
+        <v>2723</v>
       </c>
       <c r="C1341" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1341" s="3" t="s">
-        <v>2722</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="1342" spans="1:4">
       <c r="A1342" s="2" t="s">
-        <v>2727</v>
+        <v>2724</v>
       </c>
       <c r="B1342" s="2" t="s">
-        <v>2728</v>
+        <v>2725</v>
       </c>
       <c r="C1342" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1342" s="3" t="s">
         <v>8</v>
@@ -27798,293 +27799,293 @@
     </row>
     <row r="1343" spans="1:4">
       <c r="A1343" s="2" t="s">
-        <v>2729</v>
+        <v>2726</v>
       </c>
       <c r="B1343" s="2" t="s">
-        <v>2730</v>
+        <v>2727</v>
       </c>
       <c r="C1343" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1343" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1344" spans="1:4">
       <c r="A1344" s="2" t="s">
-        <v>2731</v>
+        <v>2728</v>
       </c>
       <c r="B1344" s="2" t="s">
-        <v>2732</v>
+        <v>2729</v>
       </c>
       <c r="C1344" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1344" s="3" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1345" spans="1:4">
       <c r="A1345" s="2" t="s">
-        <v>2734</v>
+        <v>2731</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>2735</v>
+        <v>2732</v>
       </c>
       <c r="C1345" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1345" s="3" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1346" spans="1:4">
       <c r="A1346" s="2" t="s">
-        <v>2736</v>
+        <v>2733</v>
       </c>
       <c r="B1346" s="2" t="s">
-        <v>2737</v>
+        <v>2734</v>
       </c>
       <c r="C1346" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1346" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1347" spans="1:4">
       <c r="A1347" s="2" t="s">
-        <v>2738</v>
+        <v>2735</v>
       </c>
       <c r="B1347" s="2" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
       <c r="C1347" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1347" s="3" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1348" spans="1:4">
       <c r="A1348" s="2" t="s">
-        <v>2740</v>
+        <v>2737</v>
       </c>
       <c r="B1348" s="2" t="s">
-        <v>2741</v>
+        <v>2738</v>
       </c>
       <c r="C1348" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1348" s="3" t="s">
-        <v>2835</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="1349" spans="1:4">
       <c r="A1349" s="2" t="s">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="B1349" s="2" t="s">
         <v>1515</v>
       </c>
       <c r="C1349" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1349" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1350" spans="1:4">
       <c r="A1350" s="2" t="s">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="B1350" s="2" t="s">
-        <v>2744</v>
+        <v>2741</v>
       </c>
       <c r="C1350" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1350" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1351" spans="1:4">
       <c r="A1351" s="2" t="s">
-        <v>2745</v>
+        <v>2742</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>2746</v>
+        <v>2743</v>
       </c>
       <c r="C1351" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1351" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1352" spans="1:4">
       <c r="A1352" s="2" t="s">
-        <v>2747</v>
+        <v>2744</v>
       </c>
       <c r="B1352" s="2" t="s">
-        <v>2748</v>
+        <v>2745</v>
       </c>
       <c r="C1352" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1352" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1353" spans="1:4">
       <c r="A1353" s="2" t="s">
-        <v>2749</v>
+        <v>2746</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>2750</v>
+        <v>2747</v>
       </c>
       <c r="C1353" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1353" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1354" spans="1:4">
       <c r="A1354" s="2" t="s">
-        <v>2751</v>
+        <v>2748</v>
       </c>
       <c r="B1354" s="2" t="s">
-        <v>2752</v>
+        <v>2749</v>
       </c>
       <c r="C1354" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1354" s="3" t="s">
-        <v>2845</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="1355" spans="1:4">
       <c r="A1355" s="2" t="s">
-        <v>2753</v>
+        <v>2750</v>
       </c>
       <c r="B1355" s="2" t="s">
-        <v>2754</v>
+        <v>2751</v>
       </c>
       <c r="C1355" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1355" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1356" spans="1:4">
       <c r="A1356" s="2" t="s">
-        <v>2755</v>
+        <v>2752</v>
       </c>
       <c r="B1356" s="2" t="s">
-        <v>2756</v>
+        <v>2753</v>
       </c>
       <c r="C1356" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1356" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1357" spans="1:4">
       <c r="A1357" s="2" t="s">
-        <v>2757</v>
+        <v>2754</v>
       </c>
       <c r="B1357" s="2" t="s">
-        <v>2758</v>
+        <v>2755</v>
       </c>
       <c r="C1357" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1357" s="3" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1358" spans="1:4">
       <c r="A1358" s="2" t="s">
-        <v>2759</v>
+        <v>2756</v>
       </c>
       <c r="B1358" s="2" t="s">
-        <v>2760</v>
+        <v>2757</v>
       </c>
       <c r="C1358" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1358" s="3" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1359" spans="1:4">
       <c r="A1359" s="2" t="s">
-        <v>2761</v>
+        <v>2758</v>
       </c>
       <c r="B1359" s="2" t="s">
         <v>825</v>
       </c>
       <c r="C1359" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1359" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1360" spans="1:4">
       <c r="A1360" s="2" t="s">
-        <v>2762</v>
+        <v>2759</v>
       </c>
       <c r="B1360" s="2" t="s">
-        <v>2763</v>
+        <v>2760</v>
       </c>
       <c r="C1360" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1360" s="3" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1361" spans="1:4">
       <c r="A1361" s="2" t="s">
-        <v>2764</v>
+        <v>2761</v>
       </c>
       <c r="B1361" s="2" t="s">
-        <v>2765</v>
+        <v>2762</v>
       </c>
       <c r="C1361" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1361" s="3" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1362" spans="1:4">
       <c r="A1362" s="2" t="s">
-        <v>2766</v>
+        <v>2763</v>
       </c>
       <c r="B1362" s="2" t="s">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="C1362" s="3" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="D1362" s="3" t="s">
-        <v>2719</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="1363" spans="1:4">
       <c r="A1363" s="2" t="s">
-        <v>2767</v>
+        <v>2764</v>
       </c>
       <c r="B1363" s="2" t="s">
-        <v>2768</v>
+        <v>2765</v>
       </c>
       <c r="C1363" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1363" s="3" t="s">
         <v>38</v>
@@ -28092,13 +28093,13 @@
     </row>
     <row r="1364" spans="1:4">
       <c r="A1364" s="2" t="s">
-        <v>2770</v>
+        <v>2767</v>
       </c>
       <c r="B1364" s="2" t="s">
-        <v>2771</v>
+        <v>2768</v>
       </c>
       <c r="C1364" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1364" s="3" t="s">
         <v>38</v>
@@ -28106,13 +28107,13 @@
     </row>
     <row r="1365" spans="1:4">
       <c r="A1365" s="2" t="s">
-        <v>2772</v>
+        <v>2769</v>
       </c>
       <c r="B1365" s="2" t="s">
-        <v>2773</v>
+        <v>2770</v>
       </c>
       <c r="C1365" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1365" s="3" t="s">
         <v>38</v>
@@ -28120,13 +28121,13 @@
     </row>
     <row r="1366" spans="1:4">
       <c r="A1366" s="2" t="s">
-        <v>2774</v>
+        <v>2771</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>2775</v>
+        <v>2772</v>
       </c>
       <c r="C1366" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1366" s="3" t="s">
         <v>38</v>
@@ -28134,13 +28135,13 @@
     </row>
     <row r="1367" spans="1:4">
       <c r="A1367" s="2" t="s">
-        <v>2776</v>
+        <v>2773</v>
       </c>
       <c r="B1367" s="2" t="s">
-        <v>2777</v>
+        <v>2774</v>
       </c>
       <c r="C1367" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1367" s="3" t="s">
         <v>8</v>
@@ -28148,13 +28149,13 @@
     </row>
     <row r="1368" spans="1:4">
       <c r="A1368" s="2" t="s">
-        <v>2778</v>
+        <v>2775</v>
       </c>
       <c r="B1368" s="2" t="s">
-        <v>2779</v>
+        <v>2776</v>
       </c>
       <c r="C1368" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1368" s="3" t="s">
         <v>58</v>
@@ -28162,13 +28163,13 @@
     </row>
     <row r="1369" spans="1:4">
       <c r="A1369" s="2" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="B1369" s="2" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="C1369" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1369" s="3" t="s">
         <v>58</v>
@@ -28176,13 +28177,13 @@
     </row>
     <row r="1370" spans="1:4">
       <c r="A1370" s="2" t="s">
-        <v>2782</v>
+        <v>2779</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>2783</v>
+        <v>2780</v>
       </c>
       <c r="C1370" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1370" s="3" t="s">
         <v>58</v>
@@ -28190,13 +28191,13 @@
     </row>
     <row r="1371" spans="1:4">
       <c r="A1371" s="2" t="s">
-        <v>2784</v>
+        <v>2781</v>
       </c>
       <c r="B1371" s="2" t="s">
-        <v>2785</v>
+        <v>2782</v>
       </c>
       <c r="C1371" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1371" s="3" t="s">
         <v>58</v>
@@ -28204,27 +28205,27 @@
     </row>
     <row r="1372" spans="1:4">
       <c r="A1372" s="2" t="s">
-        <v>2786</v>
+        <v>2783</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>2787</v>
+        <v>2784</v>
       </c>
       <c r="C1372" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1372" s="3" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1373" spans="1:4">
       <c r="A1373" s="2" t="s">
-        <v>2788</v>
+        <v>2785</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>2789</v>
+        <v>2786</v>
       </c>
       <c r="C1373" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1373" s="3" t="s">
         <v>58</v>
@@ -28232,13 +28233,13 @@
     </row>
     <row r="1374" spans="1:4">
       <c r="A1374" s="2" t="s">
-        <v>2790</v>
+        <v>2787</v>
       </c>
       <c r="B1374" s="2" t="s">
-        <v>2791</v>
+        <v>2788</v>
       </c>
       <c r="C1374" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1374" s="3" t="s">
         <v>58</v>
@@ -28246,13 +28247,13 @@
     </row>
     <row r="1375" spans="1:4">
       <c r="A1375" s="2" t="s">
-        <v>2792</v>
+        <v>2789</v>
       </c>
       <c r="B1375" s="2" t="s">
-        <v>2793</v>
+        <v>2790</v>
       </c>
       <c r="C1375" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1375" s="3" t="s">
         <v>58</v>
@@ -28260,13 +28261,13 @@
     </row>
     <row r="1376" spans="1:4">
       <c r="A1376" s="2" t="s">
-        <v>2794</v>
+        <v>2791</v>
       </c>
       <c r="B1376" s="2" t="s">
-        <v>2795</v>
+        <v>2792</v>
       </c>
       <c r="C1376" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1376" s="3" t="s">
         <v>161</v>
@@ -28274,27 +28275,27 @@
     </row>
     <row r="1377" spans="1:4">
       <c r="A1377" s="2" t="s">
-        <v>2796</v>
+        <v>2793</v>
       </c>
       <c r="B1377" s="2" t="s">
-        <v>2797</v>
+        <v>2794</v>
       </c>
       <c r="C1377" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1377" s="3" t="s">
-        <v>2798</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="1378" spans="1:4">
       <c r="A1378" s="2" t="s">
-        <v>2799</v>
+        <v>2796</v>
       </c>
       <c r="B1378" s="2" t="s">
-        <v>2800</v>
+        <v>2797</v>
       </c>
       <c r="C1378" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1378" s="3" t="s">
         <v>38</v>
@@ -28302,13 +28303,13 @@
     </row>
     <row r="1379" spans="1:4">
       <c r="A1379" s="2" t="s">
-        <v>2801</v>
+        <v>2798</v>
       </c>
       <c r="B1379" s="2" t="s">
-        <v>2802</v>
+        <v>2799</v>
       </c>
       <c r="C1379" s="3" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D1379" s="3" t="s">
         <v>58</v>
@@ -28316,13 +28317,13 @@
     </row>
     <row r="1380" spans="1:4">
       <c r="A1380" s="2" t="s">
-        <v>2803</v>
+        <v>2800</v>
       </c>
       <c r="B1380" s="2" t="s">
-        <v>2804</v>
+        <v>2801</v>
       </c>
       <c r="C1380" s="3" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="D1380" s="3" t="s">
         <v>45</v>
@@ -28330,13 +28331,13 @@
     </row>
     <row r="1381" spans="1:4">
       <c r="A1381" s="2" t="s">
-        <v>2806</v>
+        <v>2803</v>
       </c>
       <c r="B1381" s="2" t="s">
-        <v>2807</v>
+        <v>2804</v>
       </c>
       <c r="C1381" s="3" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="D1381" s="3" t="s">
         <v>8</v>
@@ -28344,13 +28345,13 @@
     </row>
     <row r="1382" spans="1:4">
       <c r="A1382" s="2" t="s">
-        <v>2808</v>
+        <v>2805</v>
       </c>
       <c r="B1382" s="2" t="s">
-        <v>2809</v>
+        <v>2806</v>
       </c>
       <c r="C1382" s="3" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="D1382" s="3" t="s">
         <v>58</v>
@@ -28358,13 +28359,13 @@
     </row>
     <row r="1383" spans="1:4">
       <c r="A1383" s="2" t="s">
-        <v>2810</v>
+        <v>2807</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>2811</v>
+        <v>2808</v>
       </c>
       <c r="C1383" s="3" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="D1383" s="3" t="s">
         <v>58</v>
@@ -28372,13 +28373,13 @@
     </row>
     <row r="1384" spans="1:4">
       <c r="A1384" s="2" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="B1384" s="2" t="s">
-        <v>2813</v>
+        <v>2810</v>
       </c>
       <c r="C1384" s="3" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="D1384" s="3" t="s">
         <v>58</v>
@@ -28386,13 +28387,13 @@
     </row>
     <row r="1385" spans="1:4">
       <c r="A1385" s="2" t="s">
-        <v>2814</v>
+        <v>2811</v>
       </c>
       <c r="B1385" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C1385" s="3" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="D1385" s="3" t="s">
         <v>174</v>
@@ -28400,13 +28401,13 @@
     </row>
     <row r="1386" spans="1:4">
       <c r="A1386" s="2" t="s">
-        <v>2815</v>
+        <v>2812</v>
       </c>
       <c r="B1386" s="2" t="s">
-        <v>2816</v>
+        <v>2813</v>
       </c>
       <c r="C1386" s="3" t="s">
-        <v>2817</v>
+        <v>2814</v>
       </c>
       <c r="D1386" s="3" t="s">
         <v>45</v>
@@ -28414,13 +28415,13 @@
     </row>
     <row r="1387" spans="1:4">
       <c r="A1387" s="2" t="s">
-        <v>2818</v>
+        <v>2815</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>2819</v>
+        <v>2816</v>
       </c>
       <c r="C1387" s="3" t="s">
-        <v>2817</v>
+        <v>2814</v>
       </c>
       <c r="D1387" s="3" t="s">
         <v>38</v>
@@ -28428,13 +28429,13 @@
     </row>
     <row r="1388" spans="1:4">
       <c r="A1388" s="2" t="s">
-        <v>2820</v>
+        <v>2817</v>
       </c>
       <c r="B1388" s="2" t="s">
-        <v>2821</v>
+        <v>2818</v>
       </c>
       <c r="C1388" s="3" t="s">
-        <v>2817</v>
+        <v>2814</v>
       </c>
       <c r="D1388" s="3" t="s">
         <v>38</v>
@@ -28442,13 +28443,13 @@
     </row>
     <row r="1389" spans="1:4">
       <c r="A1389" s="2" t="s">
-        <v>2822</v>
+        <v>2819</v>
       </c>
       <c r="B1389" s="2" t="s">
-        <v>2748</v>
+        <v>2745</v>
       </c>
       <c r="C1389" s="3" t="s">
-        <v>2817</v>
+        <v>2814</v>
       </c>
       <c r="D1389" s="3" t="s">
         <v>38</v>
